--- a/projects/AcuRev1320/demand_test/demand_test_case.xlsx
+++ b/projects/AcuRev1320/demand_test/demand_test_case.xlsx
@@ -1,49 +1,121 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YangWang\project_code\rev1320_code\autotest\test_case\AcuRev1320\demand_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZihanGao\Desktop\test_code\autotest\projects\AcuRev1320\demand_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F3F650-B3E2-43B0-8D2E-404D68D6F31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4A6236-8D27-4E63-A5C5-A7CAD4232DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="test_case_mV-1e2w1p" sheetId="14" state="hidden" r:id="rId1"/>
-    <sheet name="test_case_mA" sheetId="21" r:id="rId2"/>
-    <sheet name="test_case_mA-1e2w1p" sheetId="16" state="hidden" r:id="rId3"/>
-    <sheet name="test_data" sheetId="17" state="hidden" r:id="rId4"/>
+    <sheet name="test_case_mV-1e2w1p" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="test_case_mA" sheetId="2" r:id="rId2"/>
+    <sheet name="test_case_mA-1e2w1p" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="test_data" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="test_case_mV" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">test_case_mA!$A$1:$N$18</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="72">
   <si>
     <t>test_case</t>
   </si>
   <si>
+    <t>voltage</t>
+  </si>
+  <si>
+    <t>angle</t>
+  </si>
+  <si>
+    <t>current</t>
+  </si>
+  <si>
+    <t>wire_type</t>
+  </si>
+  <si>
+    <t>freq（Hz）</t>
+  </si>
+  <si>
+    <t>demand_method</t>
+  </si>
+  <si>
+    <t>interval</t>
+  </si>
+  <si>
+    <t>update_rate</t>
+  </si>
+  <si>
+    <t>demand_trigger</t>
+  </si>
+  <si>
+    <t>voltage_accuracy</t>
+  </si>
+  <si>
+    <t>采样次数</t>
+  </si>
+  <si>
+    <t>采样间隔</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case1</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case2</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case3</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case4</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case5</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case6</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case7</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case8</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case9</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case10</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case11</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case12</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case13</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case14</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case15</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case16</t>
+  </si>
+  <si>
+    <t>AcuRev1320_case17</t>
+  </si>
+  <si>
     <t>Phase_A_Voltage</t>
   </si>
   <si>
@@ -92,9 +164,6 @@
     <t>频率（Hz）</t>
   </si>
   <si>
-    <t>voltage_accuracy</t>
-  </si>
-  <si>
     <t>current_accuracy</t>
   </si>
   <si>
@@ -110,18 +179,48 @@
     <t>apparent_power_accuracy</t>
   </si>
   <si>
-    <t>采样次数</t>
-  </si>
-  <si>
-    <t>采样间隔</t>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>Acuvim2v3_case98</t>
+  </si>
+  <si>
+    <t>1E2w1p</t>
+  </si>
+  <si>
+    <t>相比TP20, 偏差不超过 0.2%</t>
+  </si>
+  <si>
+    <t>Acuvim2v3_case99</t>
+  </si>
+  <si>
+    <t>相比TP21, 偏差不超过 0.4%</t>
+  </si>
+  <si>
+    <t>Acuvim2v3_case100</t>
+  </si>
+  <si>
+    <t>相比TP22, 偏差不超过 0.4%</t>
+  </si>
+  <si>
+    <t>Acuvim2v3_case101</t>
+  </si>
+  <si>
+    <t>Acuvim2v3_case102</t>
+  </si>
+  <si>
+    <t>Acuvim2v3_case103</t>
+  </si>
+  <si>
+    <t>Acuvim2v3_case104</t>
+  </si>
+  <si>
+    <t>Acuvim2v3_case105</t>
   </si>
   <si>
     <t>Acuvim2v3_case1</t>
   </si>
   <si>
-    <t>1E2w1p</t>
-  </si>
-  <si>
     <t>Acuvim2v3_case2</t>
   </si>
   <si>
@@ -141,121 +240,6 @@
   </si>
   <si>
     <t>Acuvim2v3_case8</t>
-  </si>
-  <si>
-    <t>Acuvim2v3_case98</t>
-  </si>
-  <si>
-    <t>Acuvim2v3_case99</t>
-  </si>
-  <si>
-    <t>Acuvim2v3_case100</t>
-  </si>
-  <si>
-    <t>Acuvim2v3_case101</t>
-  </si>
-  <si>
-    <t>Acuvim2v3_case102</t>
-  </si>
-  <si>
-    <t>Acuvim2v3_case103</t>
-  </si>
-  <si>
-    <t>Acuvim2v3_case104</t>
-  </si>
-  <si>
-    <t>Acuvim2v3_case105</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>相比TP20, 偏差不超过 0.2%</t>
-  </si>
-  <si>
-    <t>相比TP21, 偏差不超过 0.4%</t>
-  </si>
-  <si>
-    <t>相比TP22, 偏差不超过 0.4%</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case1</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case2</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case3</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case4</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case5</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case6</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case7</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case8</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case9</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case10</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case11</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case12</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case13</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case14</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case15</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case16</t>
-  </si>
-  <si>
-    <t>AcuRev1320_case17</t>
-  </si>
-  <si>
-    <t>voltage</t>
-  </si>
-  <si>
-    <t>angle</t>
-  </si>
-  <si>
-    <t>current</t>
-  </si>
-  <si>
-    <t>wire_type</t>
-  </si>
-  <si>
-    <t>demand_method</t>
-  </si>
-  <si>
-    <t>interval</t>
-  </si>
-  <si>
-    <t>update_rate</t>
-  </si>
-  <si>
-    <t>demand_trigger</t>
-  </si>
-  <si>
-    <t>freq（Hz）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -339,7 +323,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -359,10 +343,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -663,13 +648,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="21" max="21" width="31.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="7" customWidth="1"/>
+    <col min="21" max="21" width="31.44140625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -677,84 +662,84 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>45</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="X1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
       <c r="Z1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B2">
         <v>312.3</v>
@@ -799,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q2">
         <v>60</v>
@@ -814,7 +799,7 @@
         <v>0.1</v>
       </c>
       <c r="U2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="V2">
         <v>0</v>
@@ -829,12 +814,12 @@
         <v>0.1</v>
       </c>
       <c r="Z2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <v>312.3</v>
@@ -879,7 +864,7 @@
         <v>0.5</v>
       </c>
       <c r="P3" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q3">
         <v>60</v>
@@ -894,7 +879,7 @@
         <v>0.1</v>
       </c>
       <c r="U3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="V3">
         <v>0</v>
@@ -909,12 +894,12 @@
         <v>0.1</v>
       </c>
       <c r="Z3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B4">
         <v>312.3</v>
@@ -959,7 +944,7 @@
         <v>-0.8</v>
       </c>
       <c r="P4" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q4">
         <v>60</v>
@@ -974,7 +959,7 @@
         <v>0.1</v>
       </c>
       <c r="U4" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -989,12 +974,12 @@
         <v>0.1</v>
       </c>
       <c r="Z4" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B5">
         <v>381.7</v>
@@ -1039,7 +1024,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q5">
         <v>60</v>
@@ -1054,7 +1039,7 @@
         <v>0.1</v>
       </c>
       <c r="U5" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -1069,12 +1054,12 @@
         <v>0.1</v>
       </c>
       <c r="Z5" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B6">
         <v>381.7</v>
@@ -1119,7 +1104,7 @@
         <v>0.5</v>
       </c>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q6">
         <v>60</v>
@@ -1134,7 +1119,7 @@
         <v>0.1</v>
       </c>
       <c r="U6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1149,12 +1134,12 @@
         <v>0.1</v>
       </c>
       <c r="Z6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B7">
         <v>381.7</v>
@@ -1199,7 +1184,7 @@
         <v>-0.8</v>
       </c>
       <c r="P7" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q7">
         <v>60</v>
@@ -1214,7 +1199,7 @@
         <v>0.1</v>
       </c>
       <c r="U7" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -1229,12 +1214,12 @@
         <v>0.1</v>
       </c>
       <c r="Z7" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B8">
         <v>347</v>
@@ -1279,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q8">
         <v>57</v>
@@ -1294,7 +1279,7 @@
         <v>0.1</v>
       </c>
       <c r="U8" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -1309,12 +1294,12 @@
         <v>0.1</v>
       </c>
       <c r="Z8" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="B9">
         <v>347</v>
@@ -1359,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q9">
         <v>63</v>
@@ -1374,7 +1359,7 @@
         <v>0.1</v>
       </c>
       <c r="U9" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -1389,7 +1374,7 @@
         <v>0.1</v>
       </c>
       <c r="Z9" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1399,19 +1384,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.5546875" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875"/>
-    <col min="6" max="6" width="20.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" customWidth="1"/>
-    <col min="9" max="9" width="17.44140625" customWidth="1"/>
-    <col min="10" max="10" width="21.5546875" customWidth="1"/>
-    <col min="11" max="11" width="26.5546875" customWidth="1"/>
+    <col min="1" max="1" width="30.5546875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="25.109375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="26.5546875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -1419,48 +1404,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="M1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="N1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B2" s="5">
         <v>200</v>
@@ -1472,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>50</v>
@@ -1481,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" s="5">
         <v>15</v>
@@ -1504,7 +1489,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="B3" s="5">
         <v>9</v>
@@ -1516,7 +1501,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>50</v>
@@ -1548,7 +1533,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5">
         <v>200</v>
@@ -1566,7 +1551,7 @@
         <v>50</v>
       </c>
       <c r="G4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="5">
         <v>10</v>
@@ -1592,7 +1577,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="B5" s="5">
         <v>200</v>
@@ -1636,7 +1621,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B6" s="5">
         <v>200</v>
@@ -1680,7 +1665,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="B7" s="5">
         <v>200</v>
@@ -1724,7 +1709,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="B8" s="5">
         <v>200</v>
@@ -1768,7 +1753,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5">
         <v>200</v>
@@ -1812,7 +1797,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="B10" s="5">
         <v>200</v>
@@ -1856,7 +1841,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="B11" s="5">
         <v>0</v>
@@ -1900,7 +1885,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="B12" s="5">
         <v>200</v>
@@ -1944,7 +1929,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="B13" s="5">
         <v>200</v>
@@ -1988,7 +1973,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="B14" s="5">
         <v>200</v>
@@ -2032,7 +2017,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="B15" s="5">
         <v>200</v>
@@ -2076,7 +2061,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="B16" s="5">
         <v>200</v>
@@ -2120,7 +2105,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="B17" s="5">
         <v>200</v>
@@ -2164,7 +2149,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="B18" s="5">
         <v>9</v>
@@ -2209,16 +2194,16 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -2226,84 +2211,84 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>45</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="X1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
       <c r="Z1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B2">
         <v>312.3</v>
@@ -2348,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q2">
         <v>60</v>
@@ -2363,7 +2348,7 @@
         <v>0.1</v>
       </c>
       <c r="U2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="V2">
         <v>0</v>
@@ -2378,12 +2363,12 @@
         <v>0.1</v>
       </c>
       <c r="Z2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <v>312.3</v>
@@ -2428,7 +2413,7 @@
         <v>0.5</v>
       </c>
       <c r="P3" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q3">
         <v>60</v>
@@ -2443,7 +2428,7 @@
         <v>0.1</v>
       </c>
       <c r="U3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="V3">
         <v>0</v>
@@ -2458,12 +2443,12 @@
         <v>0.1</v>
       </c>
       <c r="Z3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B4">
         <v>312.3</v>
@@ -2508,7 +2493,7 @@
         <v>-0.8</v>
       </c>
       <c r="P4" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q4">
         <v>60</v>
@@ -2523,7 +2508,7 @@
         <v>0.1</v>
       </c>
       <c r="U4" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -2538,12 +2523,12 @@
         <v>0.1</v>
       </c>
       <c r="Z4" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B5">
         <v>381.7</v>
@@ -2588,7 +2573,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q5">
         <v>60</v>
@@ -2603,7 +2588,7 @@
         <v>0.1</v>
       </c>
       <c r="U5" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -2618,12 +2603,12 @@
         <v>0.1</v>
       </c>
       <c r="Z5" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B6">
         <v>381.7</v>
@@ -2668,7 +2653,7 @@
         <v>0.5</v>
       </c>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q6">
         <v>60</v>
@@ -2683,7 +2668,7 @@
         <v>0.1</v>
       </c>
       <c r="U6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -2698,12 +2683,12 @@
         <v>0.1</v>
       </c>
       <c r="Z6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B7">
         <v>381.7</v>
@@ -2748,7 +2733,7 @@
         <v>-0.8</v>
       </c>
       <c r="P7" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q7">
         <v>60</v>
@@ -2763,7 +2748,7 @@
         <v>0.1</v>
       </c>
       <c r="U7" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2778,12 +2763,12 @@
         <v>0.1</v>
       </c>
       <c r="Z7" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B8">
         <v>347</v>
@@ -2828,7 +2813,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q8">
         <v>57</v>
@@ -2843,7 +2828,7 @@
         <v>0.1</v>
       </c>
       <c r="U8" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -2858,12 +2843,12 @@
         <v>0.1</v>
       </c>
       <c r="Z8" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="B9">
         <v>347</v>
@@ -2908,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q9">
         <v>63</v>
@@ -2923,7 +2908,7 @@
         <v>0.1</v>
       </c>
       <c r="U9" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2938,7 +2923,7 @@
         <v>0.1</v>
       </c>
       <c r="Z9" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2948,12 +2933,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z9"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875"/>
+    <col min="1" max="1" width="17.6640625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -2961,84 +2946,84 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>45</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="X1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
       <c r="Z1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="B2">
         <v>69</v>
@@ -3083,7 +3068,7 @@
         <v>0.5</v>
       </c>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q2">
         <v>60</v>
@@ -3115,7 +3100,7 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B3">
         <v>69</v>
@@ -3160,7 +3145,7 @@
         <v>0.5</v>
       </c>
       <c r="P3" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q3">
         <v>60</v>
@@ -3192,7 +3177,7 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="B4">
         <v>69</v>
@@ -3237,7 +3222,7 @@
         <v>0.5</v>
       </c>
       <c r="P4" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q4">
         <v>60</v>
@@ -3269,7 +3254,7 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <v>69</v>
@@ -3314,7 +3299,7 @@
         <v>0.5</v>
       </c>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q5">
         <v>60</v>
@@ -3346,7 +3331,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>69</v>
@@ -3391,7 +3376,7 @@
         <v>0.5</v>
       </c>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q6">
         <v>60</v>
@@ -3423,7 +3408,7 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B7">
         <v>69</v>
@@ -3468,7 +3453,7 @@
         <v>0.5</v>
       </c>
       <c r="P7" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q7">
         <v>60</v>
@@ -3500,7 +3485,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="B8">
         <v>69</v>
@@ -3545,7 +3530,7 @@
         <v>0.5</v>
       </c>
       <c r="P8" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q8">
         <v>60</v>
@@ -3577,7 +3562,7 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="B9">
         <v>69</v>
@@ -3622,7 +3607,7 @@
         <v>0.5</v>
       </c>
       <c r="P9" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="Q9">
         <v>60</v>
@@ -3649,6 +3634,809 @@
         <v>3000</v>
       </c>
       <c r="Y9">
+        <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>200</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>50</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>15</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0.01</v>
+      </c>
+      <c r="L2">
+        <v>50</v>
+      </c>
+      <c r="M2">
+        <v>20</v>
+      </c>
+      <c r="N2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>50</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>15</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0.01</v>
+      </c>
+      <c r="L3">
+        <v>50</v>
+      </c>
+      <c r="M3">
+        <v>20</v>
+      </c>
+      <c r="N3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>200</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0.01</v>
+      </c>
+      <c r="L4">
+        <v>50</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
+      </c>
+      <c r="N4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>200</v>
+      </c>
+      <c r="C5">
+        <v>30</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0.01</v>
+      </c>
+      <c r="L5">
+        <v>50</v>
+      </c>
+      <c r="M5">
+        <v>20</v>
+      </c>
+      <c r="N5">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>200</v>
+      </c>
+      <c r="C6">
+        <v>120</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>0.01</v>
+      </c>
+      <c r="L6">
+        <v>50</v>
+      </c>
+      <c r="M6">
+        <v>20</v>
+      </c>
+      <c r="N6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>200</v>
+      </c>
+      <c r="C7">
+        <v>120</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>30</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>0.01</v>
+      </c>
+      <c r="L7">
+        <v>50</v>
+      </c>
+      <c r="M7">
+        <v>20</v>
+      </c>
+      <c r="N7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>200</v>
+      </c>
+      <c r="C8">
+        <v>210</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0.01</v>
+      </c>
+      <c r="L8">
+        <v>50</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+      <c r="N8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>200</v>
+      </c>
+      <c r="C9">
+        <v>330</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+      <c r="I9">
+        <v>15</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0.01</v>
+      </c>
+      <c r="L9">
+        <v>50</v>
+      </c>
+      <c r="M9">
+        <v>20</v>
+      </c>
+      <c r="N9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>200</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>15</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.01</v>
+      </c>
+      <c r="L10">
+        <v>50</v>
+      </c>
+      <c r="M10">
+        <v>20</v>
+      </c>
+      <c r="N10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>15</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0.01</v>
+      </c>
+      <c r="L11">
+        <v>50</v>
+      </c>
+      <c r="M11">
+        <v>20</v>
+      </c>
+      <c r="N11">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>200</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>50</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0.01</v>
+      </c>
+      <c r="L12">
+        <v>50</v>
+      </c>
+      <c r="M12">
+        <v>20</v>
+      </c>
+      <c r="N12">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
+        <v>200</v>
+      </c>
+      <c r="C13">
+        <v>30</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>15</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0.01</v>
+      </c>
+      <c r="L13">
+        <v>50</v>
+      </c>
+      <c r="M13">
+        <v>20</v>
+      </c>
+      <c r="N13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
+        <v>200</v>
+      </c>
+      <c r="C14">
+        <v>120</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>50</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>5</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>0.01</v>
+      </c>
+      <c r="L14">
+        <v>50</v>
+      </c>
+      <c r="M14">
+        <v>20</v>
+      </c>
+      <c r="N14">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
+        <v>200</v>
+      </c>
+      <c r="C15">
+        <v>210</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>50</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>0.01</v>
+      </c>
+      <c r="L15">
+        <v>50</v>
+      </c>
+      <c r="M15">
+        <v>20</v>
+      </c>
+      <c r="N15">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
+        <v>200</v>
+      </c>
+      <c r="C16">
+        <v>330</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>50</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>30</v>
+      </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <v>0.01</v>
+      </c>
+      <c r="L16">
+        <v>50</v>
+      </c>
+      <c r="M16">
+        <v>20</v>
+      </c>
+      <c r="N16">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
+        <v>200</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>50</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>5</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0.01</v>
+      </c>
+      <c r="L17">
+        <v>50</v>
+      </c>
+      <c r="M17">
+        <v>20</v>
+      </c>
+      <c r="N17">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <v>50</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0.01</v>
+      </c>
+      <c r="L18">
+        <v>50</v>
+      </c>
+      <c r="M18">
+        <v>20</v>
+      </c>
+      <c r="N18">
         <v>0.1</v>
       </c>
     </row>
